--- a/worked_examples/AIHE-CASE02_readmission_model_readiness_and_data_fitness_assessment/workbook/xlsx/AIHE-CASE02_worked_example_and_template.xlsx
+++ b/worked_examples/AIHE-CASE02_readmission_model_readiness_and_data_fitness_assessment/workbook/xlsx/AIHE-CASE02_worked_example_and_template.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Guide" sheetId="1" r:id="R6e0862745d244cf5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Worked Inputs" sheetId="2" r:id="R6bbf5bb7d6f54373"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Blank Template" sheetId="3" r:id="Ra3fdda38c87d48d7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decision Summary" sheetId="4" r:id="R3b76c5b91d484feb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Guide" sheetId="1" r:id="Rd0d8a8accc3d4561"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Worked Inputs" sheetId="2" r:id="Ra0868156389c4e34"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Blank Template" sheetId="3" r:id="Rf814aac993064580"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decision Summary" sheetId="4" r:id="R435ec7c87baf4b19"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -16,7 +16,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:fonts count="5">
+  <x:fonts count="6">
     <x:font>
       <x:sz val="11"/>
       <x:name val="Carlito"/>
@@ -44,8 +44,14 @@
       <x:sz val="11"/>
       <x:name val="Carlito"/>
     </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="11"/>
+      <x:color rgb="FF303236"/>
+      <x:name val="Carlito"/>
+    </x:font>
   </x:fonts>
-  <x:fills count="7">
+  <x:fills count="9">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -77,6 +83,16 @@
         <x:fgColor rgb="FFFFF3CD"/>
       </x:patternFill>
     </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF6B2230"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFF5F0E7"/>
+      </x:patternFill>
+    </x:fill>
   </x:fills>
   <x:borders count="38">
     <x:border/>
@@ -397,7 +413,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="109">
+  <x:cellXfs count="128">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -406,7 +422,7 @@
       <x:alignment wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="centre" wrapText="1"/>
+      <x:alignment wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -414,7 +430,7 @@
       <x:alignment wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="centre" wrapText="1"/>
+      <x:alignment wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -431,22 +447,22 @@
       <x:alignment wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="centre" wrapText="1"/>
+      <x:alignment wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="centre" wrapText="1"/>
+      <x:alignment wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="centre" wrapText="1"/>
+      <x:alignment wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="centre" vertical="centre" wrapText="1"/>
+      <x:alignment wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="centre" vertical="centre" wrapText="1"/>
+      <x:alignment wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="centre" vertical="centre" wrapText="1"/>
+      <x:alignment wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -463,22 +479,22 @@
       <x:alignment wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="2" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="centre" wrapText="1"/>
+      <x:alignment wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="2" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="centre" wrapText="1"/>
+      <x:alignment wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="2" fillId="3" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="centre" wrapText="1"/>
+      <x:alignment wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="2" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="centre" vertical="centre" wrapText="1"/>
+      <x:alignment wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="2" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="centre" vertical="centre" wrapText="1"/>
+      <x:alignment wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="2" fillId="3" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="centre" vertical="centre" wrapText="1"/>
+      <x:alignment wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
@@ -523,22 +539,22 @@
       <x:alignment wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="2" fillId="3" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="centre" wrapText="1"/>
+      <x:alignment wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="2" fillId="3" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="centre" wrapText="1"/>
+      <x:alignment wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="2" fillId="3" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="centre" wrapText="1"/>
+      <x:alignment wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="2" fillId="3" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="centre" vertical="centre" wrapText="1"/>
+      <x:alignment wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="2" fillId="3" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="centre" vertical="centre" wrapText="1"/>
+      <x:alignment wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="2" fillId="3" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="centre" vertical="centre" wrapText="1"/>
+      <x:alignment wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="2" fillId="3" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="2" fillId="3" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -553,22 +569,22 @@
       <x:alignment wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="2" fillId="3" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="centre" wrapText="1"/>
+      <x:alignment wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="2" fillId="3" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="centre" wrapText="1"/>
+      <x:alignment wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="2" fillId="3" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="centre" wrapText="1"/>
+      <x:alignment wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="2" fillId="3" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="centre" vertical="centre" wrapText="1"/>
+      <x:alignment wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="2" fillId="3" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="centre" vertical="centre" wrapText="1"/>
+      <x:alignment wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="2" fillId="3" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="centre" vertical="centre" wrapText="1"/>
+      <x:alignment wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="top" wrapText="1"/>
@@ -623,20 +639,20 @@
       <x:alignment wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="2" fillId="3" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="centre" wrapText="1"/>
+      <x:alignment wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="2" fillId="3" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="centre" vertical="centre" wrapText="1"/>
+      <x:alignment wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="2" fillId="3" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="2" fillId="3" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="2" fillId="3" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="centre" wrapText="1"/>
+      <x:alignment wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="2" fillId="3" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="centre" vertical="centre" wrapText="1"/>
+      <x:alignment wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -659,6 +675,59 @@
     <x:xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="4" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="4" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="8" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="8" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="8" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="8" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="8" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="8" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="8" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="8" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="8" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="8" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="8" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="8" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="8" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="8" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
   </x:cellXfs>
@@ -711,9 +780,9 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri"/>
-        <a:ea typeface="Calibri"/>
-        <a:cs typeface="Calibri"/>
+        <a:latin typeface="Calibri Light"/>
+        <a:ea typeface="Calibri Light"/>
+        <a:cs typeface="Calibri Light"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -822,25 +891,25 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1">
-      <x:c r="A1" s="5" t="str">
+      <x:c r="A1" s="110" t="str">
         <x:v>Readmission-Model Readiness and Data-Fitness Assessment</x:v>
       </x:c>
-      <x:c r="B1" s="5"/>
-      <x:c r="C1" s="5"/>
-      <x:c r="D1" s="5"/>
-      <x:c r="E1" s="5"/>
-      <x:c r="F1" s="5"/>
+      <x:c r="B1" s="110"/>
+      <x:c r="C1" s="110"/>
+      <x:c r="D1" s="110"/>
+      <x:c r="E1" s="110"/>
+      <x:c r="F1" s="110"/>
     </x:row>
     <x:row r="2">
-      <x:c r="A2" s="5"/>
-      <x:c r="B2" s="5"/>
-      <x:c r="C2" s="5"/>
-      <x:c r="D2" s="5"/>
-      <x:c r="E2" s="5"/>
-      <x:c r="F2" s="5"/>
+      <x:c r="A2" s="110"/>
+      <x:c r="B2" s="110"/>
+      <x:c r="C2" s="110"/>
+      <x:c r="D2" s="110"/>
+      <x:c r="E2" s="110"/>
+      <x:c r="F2" s="110"/>
     </x:row>
     <x:row r="4">
-      <x:c r="A4" s="21" t="str">
+      <x:c r="A4" s="112" t="str">
         <x:v>Example ID</x:v>
       </x:c>
       <x:c r="B4" s="42" t="str">
@@ -848,7 +917,7 @@
       </x:c>
     </x:row>
     <x:row r="5">
-      <x:c r="A5" s="22" t="str">
+      <x:c r="A5" s="114" t="str">
         <x:v>Chapter</x:v>
       </x:c>
       <x:c r="B5" s="43" t="str">
@@ -856,7 +925,7 @@
       </x:c>
     </x:row>
     <x:row r="6">
-      <x:c r="A6" s="22" t="str">
+      <x:c r="A6" s="114" t="str">
         <x:v>Decision question</x:v>
       </x:c>
       <x:c r="B6" s="43" t="str">
@@ -864,7 +933,7 @@
       </x:c>
     </x:row>
     <x:row r="7">
-      <x:c r="A7" s="22" t="str">
+      <x:c r="A7" s="114" t="str">
         <x:v>Status</x:v>
       </x:c>
       <x:c r="B7" s="43" t="str">
@@ -872,7 +941,7 @@
       </x:c>
     </x:row>
     <x:row r="8">
-      <x:c r="A8" s="22" t="str">
+      <x:c r="A8" s="114" t="str">
         <x:v>Version</x:v>
       </x:c>
       <x:c r="B8" s="43" t="str">
@@ -880,7 +949,7 @@
       </x:c>
     </x:row>
     <x:row r="9">
-      <x:c r="A9" s="22" t="str">
+      <x:c r="A9" s="114" t="str">
         <x:v>Release date</x:v>
       </x:c>
       <x:c r="B9" s="43" t="str">
@@ -888,7 +957,7 @@
       </x:c>
     </x:row>
     <x:row r="10">
-      <x:c r="A10" s="22" t="str">
+      <x:c r="A10" s="114" t="str">
         <x:v>How to use</x:v>
       </x:c>
       <x:c r="B10" s="43" t="str">
@@ -896,7 +965,7 @@
       </x:c>
     </x:row>
     <x:row r="11">
-      <x:c r="A11" s="22" t="str">
+      <x:c r="A11" s="114" t="str">
         <x:v>Related resources</x:v>
       </x:c>
       <x:c r="B11" s="43" t="str">
@@ -904,7 +973,7 @@
       </x:c>
     </x:row>
     <x:row r="12">
-      <x:c r="A12" s="23" t="str">
+      <x:c r="A12" s="116" t="str">
         <x:v>Data protection</x:v>
       </x:c>
       <x:c r="B12" s="44" t="str">
@@ -933,38 +1002,38 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1">
-      <x:c r="A1" s="5" t="str">
+      <x:c r="A1" s="110" t="str">
         <x:v>Worked synthetic inputs and calculations</x:v>
       </x:c>
-      <x:c r="B1" s="5"/>
-      <x:c r="C1" s="5"/>
-      <x:c r="D1" s="5"/>
-      <x:c r="E1" s="5"/>
-      <x:c r="F1" s="5"/>
-      <x:c r="G1" s="5"/>
-      <x:c r="H1" s="5"/>
-      <x:c r="I1" s="5"/>
+      <x:c r="B1" s="110"/>
+      <x:c r="C1" s="110"/>
+      <x:c r="D1" s="110"/>
+      <x:c r="E1" s="110"/>
+      <x:c r="F1" s="110"/>
+      <x:c r="G1" s="110"/>
+      <x:c r="H1" s="110"/>
+      <x:c r="I1" s="110"/>
     </x:row>
     <x:row r="3">
-      <x:c r="A3" s="57" t="str">
+      <x:c r="A3" s="121" t="str">
         <x:v>Domain</x:v>
       </x:c>
-      <x:c r="B3" s="58" t="str">
+      <x:c r="B3" s="122" t="str">
         <x:v>Score (0-4)</x:v>
       </x:c>
-      <x:c r="C3" s="58" t="str">
+      <x:c r="C3" s="122" t="str">
         <x:v>Critical</x:v>
       </x:c>
-      <x:c r="D3" s="59" t="str">
+      <x:c r="D3" s="123" t="str">
         <x:v>Evidence</x:v>
       </x:c>
-      <x:c r="E3" s="91" t="str">
+      <x:c r="E3" s="124" t="str">
         <x:v>Critical failure</x:v>
       </x:c>
-      <x:c r="G3" s="57" t="str">
+      <x:c r="G3" s="121" t="str">
         <x:v>Summary</x:v>
       </x:c>
-      <x:c r="H3" s="59" t="str">
+      <x:c r="H3" s="123" t="str">
         <x:v>Formula result</x:v>
       </x:c>
     </x:row>
@@ -1163,7 +1232,7 @@
     </x:row>
     <x:row r="14">
       <x:c r="A14" s="77" t="str">
-        <x:v>Circularity and sustainability</x:v>
+        <x:v>Continuing support and service sustainability</x:v>
       </x:c>
       <x:c r="B14" s="78" t="n">
         <x:v>1</x:v>
@@ -1197,24 +1266,24 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1">
-      <x:c r="A1" s="5" t="str">
+      <x:c r="A1" s="110" t="str">
         <x:v>Blank template - replace synthetic values with governed local evidence</x:v>
       </x:c>
-      <x:c r="B1" s="5"/>
-      <x:c r="C1" s="5"/>
-      <x:c r="D1" s="5"/>
+      <x:c r="B1" s="110"/>
+      <x:c r="C1" s="110"/>
+      <x:c r="D1" s="110"/>
     </x:row>
     <x:row r="3">
-      <x:c r="A3" s="57" t="str">
+      <x:c r="A3" s="121" t="str">
         <x:v>Domain</x:v>
       </x:c>
-      <x:c r="B3" s="58" t="str">
+      <x:c r="B3" s="122" t="str">
         <x:v>Score (0-4)</x:v>
       </x:c>
-      <x:c r="C3" s="58" t="str">
+      <x:c r="C3" s="122" t="str">
         <x:v>Critical</x:v>
       </x:c>
-      <x:c r="D3" s="59" t="str">
+      <x:c r="D3" s="123" t="str">
         <x:v>Evidence</x:v>
       </x:c>
     </x:row>
@@ -1340,7 +1409,7 @@
     </x:row>
     <x:row r="14">
       <x:c r="A14" s="77" t="str">
-        <x:v>Circularity and sustainability</x:v>
+        <x:v>Continuing support and service sustainability</x:v>
       </x:c>
       <x:c r="B14" s="78" t="str"/>
       <x:c r="C14" s="78" t="str">
@@ -1371,28 +1440,28 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1">
-      <x:c r="A1" s="5" t="str">
+      <x:c r="A1" s="110" t="str">
         <x:v>Readmission-Model Readiness and Data-Fitness Assessment</x:v>
       </x:c>
-      <x:c r="B1" s="5"/>
-      <x:c r="C1" s="5"/>
-      <x:c r="D1" s="5"/>
-      <x:c r="E1" s="5"/>
-      <x:c r="F1" s="5"/>
+      <x:c r="B1" s="110"/>
+      <x:c r="C1" s="110"/>
+      <x:c r="D1" s="110"/>
+      <x:c r="E1" s="110"/>
+      <x:c r="F1" s="110"/>
     </x:row>
     <x:row r="2">
-      <x:c r="A2" s="5"/>
-      <x:c r="B2" s="5"/>
-      <x:c r="C2" s="5"/>
-      <x:c r="D2" s="5"/>
-      <x:c r="E2" s="5"/>
-      <x:c r="F2" s="5"/>
+      <x:c r="A2" s="110"/>
+      <x:c r="B2" s="110"/>
+      <x:c r="C2" s="110"/>
+      <x:c r="D2" s="110"/>
+      <x:c r="E2" s="110"/>
+      <x:c r="F2" s="110"/>
     </x:row>
     <x:row r="4">
-      <x:c r="A4" s="57" t="str">
+      <x:c r="A4" s="121" t="str">
         <x:v>Reference metric</x:v>
       </x:c>
-      <x:c r="B4" s="59" t="str">
+      <x:c r="B4" s="123" t="str">
         <x:v>Synthetic result</x:v>
       </x:c>
     </x:row>
@@ -1421,66 +1490,66 @@
       </x:c>
     </x:row>
     <x:row r="9">
-      <x:c r="A9" s="97" t="str">
+      <x:c r="A9" s="125" t="str">
         <x:v>Worked interpretation</x:v>
       </x:c>
-      <x:c r="B9" s="97"/>
-      <x:c r="C9" s="97"/>
-      <x:c r="D9" s="97"/>
-      <x:c r="E9" s="97"/>
-      <x:c r="F9" s="97"/>
+      <x:c r="B9" s="125"/>
+      <x:c r="C9" s="125"/>
+      <x:c r="D9" s="125"/>
+      <x:c r="E9" s="125"/>
+      <x:c r="F9" s="125"/>
     </x:row>
     <x:row r="10">
-      <x:c r="A10" s="102" t="str">
+      <x:c r="A10" s="126" t="str">
         <x:v>The average score suggests partial capability, but the average is not the decision rule. Interoperability and procurement readiness are critical and both fall below the minimum acceptable level. Live use should be deferred while common identifiers, versioned mappings, vendor audit and update clauses, and funded case-management capacity are established. Retrospective profiling may continue because it reduces uncertainty without creating clinical dependence.</x:v>
       </x:c>
-      <x:c r="B10" s="102"/>
-      <x:c r="C10" s="102"/>
-      <x:c r="D10" s="102"/>
-      <x:c r="E10" s="102"/>
-      <x:c r="F10" s="102"/>
+      <x:c r="B10" s="126"/>
+      <x:c r="C10" s="126"/>
+      <x:c r="D10" s="126"/>
+      <x:c r="E10" s="126"/>
+      <x:c r="F10" s="126"/>
     </x:row>
     <x:row r="11">
-      <x:c r="A11" s="102"/>
-      <x:c r="B11" s="102"/>
-      <x:c r="C11" s="102"/>
-      <x:c r="D11" s="102"/>
-      <x:c r="E11" s="102"/>
-      <x:c r="F11" s="102"/>
+      <x:c r="A11" s="126"/>
+      <x:c r="B11" s="126"/>
+      <x:c r="C11" s="126"/>
+      <x:c r="D11" s="126"/>
+      <x:c r="E11" s="126"/>
+      <x:c r="F11" s="126"/>
     </x:row>
     <x:row r="12">
-      <x:c r="A12" s="102"/>
-      <x:c r="B12" s="102"/>
-      <x:c r="C12" s="102"/>
-      <x:c r="D12" s="102"/>
-      <x:c r="E12" s="102"/>
-      <x:c r="F12" s="102"/>
+      <x:c r="A12" s="126"/>
+      <x:c r="B12" s="126"/>
+      <x:c r="C12" s="126"/>
+      <x:c r="D12" s="126"/>
+      <x:c r="E12" s="126"/>
+      <x:c r="F12" s="126"/>
     </x:row>
     <x:row r="13">
-      <x:c r="A13" s="102"/>
-      <x:c r="B13" s="102"/>
-      <x:c r="C13" s="102"/>
-      <x:c r="D13" s="102"/>
-      <x:c r="E13" s="102"/>
-      <x:c r="F13" s="102"/>
+      <x:c r="A13" s="126"/>
+      <x:c r="B13" s="126"/>
+      <x:c r="C13" s="126"/>
+      <x:c r="D13" s="126"/>
+      <x:c r="E13" s="126"/>
+      <x:c r="F13" s="126"/>
     </x:row>
     <x:row r="14">
-      <x:c r="A14" s="102"/>
-      <x:c r="B14" s="102"/>
-      <x:c r="C14" s="102"/>
-      <x:c r="D14" s="102"/>
-      <x:c r="E14" s="102"/>
-      <x:c r="F14" s="102"/>
+      <x:c r="A14" s="126"/>
+      <x:c r="B14" s="126"/>
+      <x:c r="C14" s="126"/>
+      <x:c r="D14" s="126"/>
+      <x:c r="E14" s="126"/>
+      <x:c r="F14" s="126"/>
     </x:row>
     <x:row r="16">
-      <x:c r="A16" s="108" t="str">
+      <x:c r="A16" s="127" t="str">
         <x:v>Interpret calculations with evidence quality, uncertainty, mandatory safeguards, implementation capacity, monitoring, and exit conditions.</x:v>
       </x:c>
-      <x:c r="B16" s="108"/>
-      <x:c r="C16" s="108"/>
-      <x:c r="D16" s="108"/>
-      <x:c r="E16" s="108"/>
-      <x:c r="F16" s="108"/>
+      <x:c r="B16" s="127"/>
+      <x:c r="C16" s="127"/>
+      <x:c r="D16" s="127"/>
+      <x:c r="E16" s="127"/>
+      <x:c r="F16" s="127"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
